--- a/data/Actions.xlsx
+++ b/data/Actions.xlsx
@@ -20,140 +20,1271 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="529">
-  <si>
-    <t xml:space="preserve">Blinded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charmed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deafened</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="798">
+  <si>
+    <t xml:space="preserve">Ability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acolyte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Artisan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Background</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbarian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charisma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charlatan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constitution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criminal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D:%:%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dexterity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Druid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entertainer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farmer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fighter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hermit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intelligence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merchant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paladin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rogue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sailor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scribe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sigil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soldier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorcerer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Survival</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warlock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wayfarer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wisdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">آرمور</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">آرمور ترینینگ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ArmorTraining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">آرمور کلس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ArmorClass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">آرچ میج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Archmage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">آن آرمورد دیفنس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UnarmoredDefence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ااسیمار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aasimar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ابونس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ابیلیتی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ابیلیتی اسکور</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AbilityScore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ابیلیتی اسکورز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AbilityScores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ابیلیتی مادیفار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AbilityModifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ابیلیتی مادیفایر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ابیلیتی مادیفایرز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AbilityModifiers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ابیلیتی چک</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AbilityCheck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اتک</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اتک رول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackRoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اتکز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attacks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ادونچر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adventure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ادونچرر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adventurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ارمور</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ارمور ترینینگ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ارکین تریکستر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ArcaneTrickster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">استاندارد اری</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StandardArray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">استت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">استرنث</t>
+  </si>
+  <si>
+    <t xml:space="preserve">استرنث اسکور</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StrengthScore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسپرایت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسپل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسپل اتک مادیفایر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackModifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسپل اسلات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpellSlot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسپل اسلاتز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpellSlots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسپل سیو دی‌سی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpellSaveDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسپل کستر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spellcaster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسپل کستینگ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpellCasting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسپل کستینگ کلسز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpellCastingClasses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسپل کستیگ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسپید</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسپیشیز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Species</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسکور</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسکیل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ال ان</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ال ای</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ال جی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الاینمنت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alignment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الدریچ نایت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EldritchKnight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ان</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ان ای</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ان جی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">انالایند</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unaligned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اورک</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اوریجین</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Origin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اوریجین فیت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OriginFeat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اپیک بونز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EpicBoons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اکس پی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اکسترا اتک</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExtraAttack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اکسپرینس پوینت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExperiencePoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اکسپرینس پوینتز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExperiencePoints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اکوئیپمنت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ای سی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ای سی پایه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BaseAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اینتلیجنس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اینوکیشن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invocation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اینیشیتیو</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inititive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ایول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بارد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بربریان</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بربرین</t>
+  </si>
+  <si>
+    <t xml:space="preserve">برنینگ هندز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BurningHands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بونس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بکگراند</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تریت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ترینکت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trinket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ترینینگ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Training</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تمپرری هیت پوینت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TemporaryHitPoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تو اکسترا اتکز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TwoExtraAttakcs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تیفلینگ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiefling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ثرسیتینگ بلید</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ThirstingBlade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">جاینت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">د هاب اف د مولتی ورس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دانجن مستر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DungeonMaster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دث سیوینگ ثروز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SavingThrows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دراکون رزیلینس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DragonResilience</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دراگون</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دراگون بورن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragonborn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دروید</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دمیج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دمیج رولز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DamageRolls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دورف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwarf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دکستریتی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دی سی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">دی</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">D:%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دی‌ام</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دی‌ان‌دی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">راند</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رنجد اتک</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RangedAttack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رنجر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رندوم جنریشن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RandomGeneration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">روگ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ریز دد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RaiseDead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سابکلس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subclass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سایز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سشن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Session</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سورسر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سورسرر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سی ان</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سی ای</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سی جی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سیوینگ ثرو</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SavingThrow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سیوینگ ثروز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شورت رست</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ShortRest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شیلد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">فایتر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">فایربال</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fireball</t>
+  </si>
+  <si>
+    <t xml:space="preserve">فیت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">فیتی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">فیچر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لاوفول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lawful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لاوفول ایول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LawfulEvil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لاوفول نیوچرال</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LawfulNeuteral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لاوفول گود</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LawfulGood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لایتنینگ بولت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LightingBolt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لول ۱</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مادیفایر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مادیفایرز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modifiers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مانک</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مانگ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">متریال پلین</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaterialPlane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مجیک آیتمز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MagicItems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مولتی کلس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiclass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مولتیورس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiverse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مولتیکلسینگ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiclassing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">میلی اتک</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MeleeAttack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نوم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gnome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نیوچرال</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neuteral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نیوچرال ایول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NeuteralEvil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نیوچرال گود</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NeuteralGood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هفلینگ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Halfling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هولی سیمبول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HolySymbol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هومن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هیت دای</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HitDie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هیت دایس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HitDice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هیت پوینت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HitPoints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هیت پوینت دایس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HitPointDice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هیت پوینت مکسیموم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaximumHitPoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هیت پوینتز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هیت پوینتز مکسیموم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HitPointsMaximum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وارلاک</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وارلاکی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وپن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وپنز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ویزارد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ویزدم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ویزدوم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ویزدوم اسکور</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WisdomScore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پالادین</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پراپرتی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Property</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پرایمری ابیلیتی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrimaryAbility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پرسپشن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perception</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پروفشنسی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proficiency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پروفشنسی بونس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProficiencyBonus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پروفیشنسی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پرپر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پرپرد اسپلز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PreparedSpells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پسیو پرسپشن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PassivePerception</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پلنار متروپولیس اف سیجیل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پلیر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پلیر کاراکتر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PlayerCharacter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پلیر کاراکترز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PlayerCharacters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پلینز اف اگزیستنس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PlanesOfExistence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پوینت کاست</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PointCost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پکت مجیک</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PactMagic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پکت وپن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PactWeapon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کاراکتر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Character</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کاراکتر شیت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CharacterSheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کاریزما</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کامن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Common</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کانستیتوشن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کانستیتوشن اسکور</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ConstitutionScore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کانستیتوشن مادیفایر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ConstitutionModifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کانستیتوشین</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کریچر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کریچرز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creatures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کلتروپ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caltropes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کلریک</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کلس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کلس فیچرز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassFeatures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کمپین</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کنتریپ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cantrip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کورنت هیت پوینتز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CurrentHitPoints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کیاتیک</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaotic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کیاتیک ایول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChaoticEvil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کیاتیک نیوچرال</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChaoticNeuteral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کیاتیک گود</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChaoticGood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">گابلین</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">گریفون</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Griffon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">گنوم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">گود</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good</t>
+  </si>
+  <si>
+    <t xml:space="preserve">گولیاث</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goliath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">آریاز اف افکت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AreasOfEffect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اتک رولز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackRolls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسنیک اتک</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SneakAttack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الای</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ally</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اکشن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اگزاسشن</t>
   </si>
   <si>
     <t xml:space="preserve">Exhaustion</t>
   </si>
   <si>
-    <t xml:space="preserve">Frightened</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grappled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incapacitated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invisible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paralyzed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petrified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poisoned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restrained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stunned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unconscious</t>
-  </si>
-  <si>
-    <t xml:space="preserve">آرمور کلس</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ArmorClass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">آریاز اف افکت</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AreasOfEffect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اتک</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اتک رول</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackRoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اتک رولز</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackRolls</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اتکز</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attacks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ادونچرر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adventurer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اسنیک اتک</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SneakAttack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اسپل</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اسپل اسلات</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpellSlot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الای</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ally</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اکشن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اگزاسشن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ای سی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اینیشیتیو</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inititive</t>
-  </si>
-  <si>
     <t xml:space="preserve">اینیشیتیو اوردر</t>
   </si>
   <si>
@@ -202,42 +1333,18 @@
     <t xml:space="preserve">Thunderwave</t>
   </si>
   <si>
-    <t xml:space="preserve">دمیج</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دی سی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DC</t>
-  </si>
-  <si>
     <t xml:space="preserve">دیساینگیج</t>
   </si>
   <si>
     <t xml:space="preserve">Disengage</t>
   </si>
   <si>
-    <t xml:space="preserve">دی‌ام</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DM</t>
-  </si>
-  <si>
     <t xml:space="preserve">رولز گلاسری</t>
   </si>
   <si>
     <t xml:space="preserve">RulesGlossary</t>
   </si>
   <si>
-    <t xml:space="preserve">روگ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rogue</t>
-  </si>
-  <si>
     <t xml:space="preserve">ریاکشن</t>
   </si>
   <si>
@@ -266,30 +1373,6 @@
   </si>
   <si>
     <t xml:space="preserve">Save</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سیوینگ ثرو</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SavingThrow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سیوینگ ثروز</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SavingThrows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">شیلد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">لول</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level</t>
   </si>
   <si>
     <t xml:space="preserve">مارچینگ اوردر</t>
@@ -328,21 +1411,6 @@
     <t xml:space="preserve">Natural1</t>
   </si>
   <si>
-    <t xml:space="preserve">هولی سیمبول</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HolySymbol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">هیت پوینت</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HitPoints</t>
-  </si>
-  <si>
-    <t xml:space="preserve">هیت پوینتز</t>
-  </si>
-  <si>
     <t xml:space="preserve">وارهمر</t>
   </si>
   <si>
@@ -355,12 +1423,6 @@
     <t xml:space="preserve">Vulnerability</t>
   </si>
   <si>
-    <t xml:space="preserve">وپن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon</t>
-  </si>
-  <si>
     <t xml:space="preserve">ویزدوم سیو</t>
   </si>
   <si>
@@ -370,10 +1432,7 @@
     <t xml:space="preserve">پرون</t>
   </si>
   <si>
-    <t xml:space="preserve">پلیر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Player</t>
+    <t xml:space="preserve">Prone</t>
   </si>
   <si>
     <t xml:space="preserve">پوش</t>
@@ -388,12 +1447,6 @@
     <t xml:space="preserve">PiercingDamage</t>
   </si>
   <si>
-    <t xml:space="preserve">کاراکتر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Character</t>
-  </si>
-  <si>
     <t xml:space="preserve">کاندیشن</t>
   </si>
   <si>
@@ -412,22 +1465,10 @@
     <t xml:space="preserve">CunningAction</t>
   </si>
   <si>
-    <t xml:space="preserve">کریچر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creature</t>
-  </si>
-  <si>
     <t xml:space="preserve">کستر</t>
   </si>
   <si>
     <t xml:space="preserve">Caster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">کلس</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Class</t>
   </si>
   <si>
     <t xml:space="preserve">کمبت</t>
@@ -457,27 +1498,12 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">۱۵</t>
-  </si>
-  <si>
     <t xml:space="preserve">ابجکتز</t>
   </si>
   <si>
     <t xml:space="preserve">Objects</t>
   </si>
   <si>
-    <t xml:space="preserve">ابیلیتی اسکور</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AbilityScore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ابیلیتی مادیفایر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AbilityModifier</t>
-  </si>
-  <si>
     <t xml:space="preserve">استیبل</t>
   </si>
   <si>
@@ -520,6 +1546,9 @@
     <t xml:space="preserve">بلادید</t>
   </si>
   <si>
+    <t xml:space="preserve">Blinded</t>
+  </si>
+  <si>
     <t xml:space="preserve">بلوگان</t>
   </si>
   <si>
@@ -547,21 +1576,9 @@
     <t xml:space="preserve">تمپرری هیت پونیتز</t>
   </si>
   <si>
-    <t xml:space="preserve">تمپرری هیت پوینت</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TemporaryHitPoint</t>
-  </si>
-  <si>
     <t xml:space="preserve">تمپرری هیت پوینتز</t>
   </si>
   <si>
-    <t xml:space="preserve">دانجن مستر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DungeonMaster</t>
-  </si>
-  <si>
     <t xml:space="preserve">دث</t>
   </si>
   <si>
@@ -571,9 +1588,6 @@
     <t xml:space="preserve">دث سیوینگ ثرو</t>
   </si>
   <si>
-    <t xml:space="preserve">دث سیوینگ ثروز</t>
-  </si>
-  <si>
     <t xml:space="preserve">دمجینگ افکت</t>
   </si>
   <si>
@@ -592,12 +1606,6 @@
     <t xml:space="preserve">DamageRoll</t>
   </si>
   <si>
-    <t xml:space="preserve">دمیج رولز</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DamageRolls</t>
-  </si>
-  <si>
     <t xml:space="preserve">دگر</t>
   </si>
   <si>
@@ -608,9 +1616,6 @@
   </si>
   <si>
     <t xml:space="preserve">دی ان دی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DND</t>
   </si>
   <si>
     <r>
@@ -634,9 +1639,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">D:%:%</t>
-  </si>
-  <si>
     <t xml:space="preserve">رزیستنس</t>
   </si>
   <si>
@@ -646,24 +1648,12 @@
     <t xml:space="preserve">رزیستنش</t>
   </si>
   <si>
-    <t xml:space="preserve">ریز دد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RaiseDead</t>
-  </si>
-  <si>
     <t xml:space="preserve">شورت اور لانگ رست</t>
   </si>
   <si>
     <t xml:space="preserve">ShortOrLongRest</t>
   </si>
   <si>
-    <t xml:space="preserve">شورت رست</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ShortRest</t>
-  </si>
-  <si>
     <t xml:space="preserve">فایر</t>
   </si>
   <si>
@@ -676,12 +1666,6 @@
     <t xml:space="preserve">FireDamage</t>
   </si>
   <si>
-    <t xml:space="preserve">فایربال</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fireball</t>
-  </si>
-  <si>
     <t xml:space="preserve">فایردمیج</t>
   </si>
   <si>
@@ -691,12 +1675,6 @@
     <t xml:space="preserve">LongRest</t>
   </si>
   <si>
-    <t xml:space="preserve">مادیفایر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modifier</t>
-  </si>
-  <si>
     <t xml:space="preserve">مانستر</t>
   </si>
   <si>
@@ -724,21 +1702,12 @@
     <t xml:space="preserve">مکسیموم هیت پوینت</t>
   </si>
   <si>
-    <t xml:space="preserve">MaximumHitPoint</t>
-  </si>
-  <si>
     <t xml:space="preserve">مکسیموم هیت پوینتز</t>
   </si>
   <si>
     <t xml:space="preserve">MaximumHitPoints</t>
   </si>
   <si>
-    <t xml:space="preserve">میلی اتک</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MeleeAttack</t>
-  </si>
-  <si>
     <t xml:space="preserve">نکراتیک دمیج</t>
   </si>
   <si>
@@ -754,9 +1723,6 @@
     <t xml:space="preserve">Help</t>
   </si>
   <si>
-    <t xml:space="preserve">هیت پوینت مکسیموم</t>
-  </si>
-  <si>
     <t xml:space="preserve">هیت پوینت مکسیکموم</t>
   </si>
   <si>
@@ -769,18 +1735,6 @@
     <t xml:space="preserve">ولنریبیلیتی</t>
   </si>
   <si>
-    <t xml:space="preserve">وپنز</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ویزارد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wizard</t>
-  </si>
-  <si>
     <t xml:space="preserve">ویزدوم چک</t>
   </si>
   <si>
@@ -805,24 +1759,12 @@
     <t xml:space="preserve">CriticalHits</t>
   </si>
   <si>
-    <t xml:space="preserve">کریچرز</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creatures</t>
-  </si>
-  <si>
     <t xml:space="preserve">کندیشن</t>
   </si>
   <si>
     <t xml:space="preserve">کورنت هیت پوینت</t>
   </si>
   <si>
-    <t xml:space="preserve">CurrentHitPoints</t>
-  </si>
-  <si>
-    <t xml:space="preserve">کورنت هیت پوینتز</t>
-  </si>
-  <si>
     <t xml:space="preserve">کولد دمیج</t>
   </si>
   <si>
@@ -871,24 +1813,6 @@
     <t xml:space="preserve">اسلحه</t>
   </si>
   <si>
-    <t xml:space="preserve">اسپل کستینگ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpellCasting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اسپید</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اسپیشیز</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Species</t>
-  </si>
-  <si>
     <t xml:space="preserve">ان آرمد استراک</t>
   </si>
   <si>
@@ -928,6 +1852,9 @@
     <t xml:space="preserve">اینکپسیتیتد</t>
   </si>
   <si>
+    <t xml:space="preserve">Incapacitated</t>
+  </si>
+  <si>
     <t xml:space="preserve">اینیشیتیو رول</t>
   </si>
   <si>
@@ -1003,12 +1930,6 @@
     <t xml:space="preserve">DifficultTerrain</t>
   </si>
   <si>
-    <t xml:space="preserve">راند</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Round</t>
-  </si>
-  <si>
     <t xml:space="preserve">ردی</t>
   </si>
   <si>
@@ -1024,18 +1945,12 @@
     <t xml:space="preserve">رنج اتک</t>
   </si>
   <si>
-    <t xml:space="preserve">RangedAttack</t>
-  </si>
-  <si>
     <t xml:space="preserve">رنج اتکز</t>
   </si>
   <si>
     <t xml:space="preserve">RangedAttacks</t>
   </si>
   <si>
-    <t xml:space="preserve">رنجد اتک</t>
-  </si>
-  <si>
     <t xml:space="preserve">رنجد اتکز</t>
   </si>
   <si>
@@ -1051,12 +1966,6 @@
     <t xml:space="preserve">Reach</t>
   </si>
   <si>
-    <t xml:space="preserve">سایز</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Size</t>
-  </si>
-  <si>
     <t xml:space="preserve">سایز کتگوری</t>
   </si>
   <si>
@@ -1099,12 +2008,6 @@
     <t xml:space="preserve">FlySpeed</t>
   </si>
   <si>
-    <t xml:space="preserve">فیچر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feature</t>
-  </si>
-  <si>
     <t xml:space="preserve">لانگ بو</t>
   </si>
   <si>
@@ -1171,12 +2074,6 @@
     <t xml:space="preserve">Willing</t>
   </si>
   <si>
-    <t xml:space="preserve">پلیر کاراکتر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PlayerCharacter</t>
-  </si>
-  <si>
     <t xml:space="preserve">پوزیشن</t>
   </si>
   <si>
@@ -1189,12 +2086,6 @@
     <t xml:space="preserve">Check</t>
   </si>
   <si>
-    <t xml:space="preserve">کاراکتر شیت</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CharacterSheet</t>
-  </si>
-  <si>
     <t xml:space="preserve">کاور</t>
   </si>
   <si>
@@ -1249,21 +2140,9 @@
     <t xml:space="preserve">Item</t>
   </si>
   <si>
-    <t xml:space="preserve">ابیلیتی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ability</t>
-  </si>
-  <si>
     <t xml:space="preserve">ادونتیج </t>
   </si>
   <si>
-    <t xml:space="preserve">ادونچر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adventure</t>
-  </si>
-  <si>
     <t xml:space="preserve">ادونچرینگ</t>
   </si>
   <si>
@@ -1288,24 +2167,12 @@
     <t xml:space="preserve">Stealth</t>
   </si>
   <si>
-    <t xml:space="preserve">اسپل کستر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spellcaster</t>
-  </si>
-  <si>
     <t xml:space="preserve">اکسپلوریشن</t>
   </si>
   <si>
     <t xml:space="preserve">Exploration</t>
   </si>
   <si>
-    <t xml:space="preserve">اکوئیپمنت</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equipment</t>
-  </si>
-  <si>
     <t xml:space="preserve">اینتلیجنس چک</t>
   </si>
   <si>
@@ -1351,12 +2218,6 @@
     <t xml:space="preserve">Torch</t>
   </si>
   <si>
-    <t xml:space="preserve">تول</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tool</t>
-  </si>
-  <si>
     <t xml:space="preserve">ثیوز تولز</t>
   </si>
   <si>
@@ -1375,30 +2236,6 @@
     <t xml:space="preserve">DungeonMastersGuide</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">دی</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:%</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">D:%</t>
-  </si>
-  <si>
     <t xml:space="preserve">دیسانونتیج</t>
   </si>
   <si>
@@ -1435,9 +2272,6 @@
     <t xml:space="preserve">سوروایول</t>
   </si>
   <si>
-    <t xml:space="preserve">Survival</t>
-  </si>
-  <si>
     <t xml:space="preserve">لایت</t>
   </si>
   <si>
@@ -1543,16 +2377,7 @@
     <t xml:space="preserve">پارالایزد</t>
   </si>
   <si>
-    <t xml:space="preserve">پرسپشن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perception</t>
-  </si>
-  <si>
-    <t xml:space="preserve">پروفشنسی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proficiency</t>
+    <t xml:space="preserve">Paralyzed</t>
   </si>
   <si>
     <t xml:space="preserve">پروفنشسی</t>
@@ -1570,18 +2395,6 @@
     <t xml:space="preserve">PlayerHandbook</t>
   </si>
   <si>
-    <t xml:space="preserve">کامن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Common</t>
-  </si>
-  <si>
-    <t xml:space="preserve">کانستیتوشن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Constitution</t>
-  </si>
-  <si>
     <t xml:space="preserve">کانستیتوشن سیوینگ ثرو</t>
   </si>
   <si>
@@ -1600,9 +2413,6 @@
     <t xml:space="preserve">کلتروپز</t>
   </si>
   <si>
-    <t xml:space="preserve">Caltropes</t>
-  </si>
-  <si>
     <t xml:space="preserve">کوارتراستف</t>
   </si>
   <si>
@@ -1610,9 +2420,6 @@
   </si>
   <si>
     <t xml:space="preserve">AbilityChekc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AbilityCheck</t>
   </si>
   <si>
     <t xml:space="preserve">آرکانا</t>
@@ -1961,7 +2768,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B298"/>
+  <dimension ref="A1:B463"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2040,2264 +2847,3503 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="0" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="0" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="0" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="0" t="s">
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="0" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="0" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="0" t="s">
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="0" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="0" t="s">
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="0" t="s">
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="0" t="s">
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="0" t="s">
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="s">
         <v>39</v>
-      </c>
-      <c r="B28" s="0" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="0" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="0" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B31" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B32" s="0" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B33" s="0" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B34" s="0" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B35" s="0" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B36" s="0" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37" s="0" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B38" s="0" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B39" s="0" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B40" s="0" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>102</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>104</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>125</v>
+        <v>98</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>133</v>
+        <v>106</v>
+      </c>
+      <c r="B77" s="0" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>141</v>
+        <v>115</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>143</v>
+        <v>117</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>61</v>
+        <v>123</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>0</v>
+        <v>131</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>83</v>
+        <v>151</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>85</v>
+        <v>153</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>175</v>
+        <v>21</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>67</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>186</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>188</v>
+        <v>53</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>191</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="B121" s="0" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>222</v>
+        <v>14</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>157</v>
+        <v>201</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>104</v>
+        <v>210</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>240</v>
+        <v>26</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>244</v>
+        <v>27</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>119</v>
+        <v>224</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>247</v>
+        <v>228</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="B144" s="0" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>252</v>
+        <v>33</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="B146" s="0" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
-        <v>254</v>
+        <v>233</v>
       </c>
       <c r="B147" s="0" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="B148" s="0" t="s">
-        <v>257</v>
+        <v>236</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="s">
-        <v>258</v>
+        <v>237</v>
       </c>
       <c r="B149" s="0" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
       <c r="B150" s="0" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="B151" s="0" t="s">
-        <v>263</v>
+        <v>192</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="B152" s="0" t="s">
-        <v>106</v>
+        <v>243</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="B153" s="0" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="B154" s="0" t="s">
-        <v>268</v>
+        <v>17</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="B155" s="0" t="s">
-        <v>270</v>
+        <v>248</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="B156" s="0" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="B157" s="0" t="s">
-        <v>274</v>
+        <v>250</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="s">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="B158" s="0" t="s">
-        <v>276</v>
+        <v>253</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="B159" s="0" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="B160" s="0" t="s">
-        <v>43</v>
+        <v>257</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="B161" s="0" t="s">
-        <v>45</v>
+        <v>259</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="B162" s="0" t="s">
-        <v>282</v>
+        <v>261</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
       <c r="B163" s="0" t="s">
-        <v>6</v>
+        <v>263</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="B164" s="0" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="B165" s="0" t="s">
-        <v>111</v>
+        <v>267</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="s">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="B166" s="0" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="B167" s="0" t="s">
-        <v>290</v>
+        <v>271</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="B168" s="0" t="s">
-        <v>292</v>
+        <v>23</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="B169" s="0" t="s">
-        <v>294</v>
+        <v>23</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="B170" s="0" t="s">
-        <v>296</v>
+        <v>275</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="s">
-        <v>297</v>
+        <v>276</v>
       </c>
       <c r="B171" s="0" t="s">
-        <v>298</v>
+        <v>277</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="s">
-        <v>299</v>
+        <v>278</v>
       </c>
       <c r="B172" s="0" t="s">
-        <v>300</v>
+        <v>279</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="s">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="B173" s="0" t="s">
-        <v>302</v>
+        <v>281</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>303</v>
+        <v>282</v>
       </c>
       <c r="B174" s="0" t="s">
-        <v>304</v>
+        <v>283</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="s">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="B175" s="0" t="s">
-        <v>306</v>
+        <v>285</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="s">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="B176" s="0" t="s">
-        <v>308</v>
+        <v>287</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="s">
-        <v>309</v>
+        <v>288</v>
       </c>
       <c r="B177" s="0" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
-        <v>311</v>
+        <v>290</v>
       </c>
       <c r="B178" s="0" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="s">
-        <v>313</v>
+        <v>292</v>
       </c>
       <c r="B179" s="0" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="B180" s="0" t="s">
-        <v>316</v>
+        <v>295</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="s">
-        <v>317</v>
+        <v>296</v>
       </c>
       <c r="B181" s="0" t="s">
-        <v>318</v>
+        <v>297</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="s">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="B182" s="0" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="B183" s="0" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="s">
-        <v>321</v>
+        <v>302</v>
       </c>
       <c r="B184" s="0" t="s">
-        <v>322</v>
+        <v>303</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="B185" s="0" t="s">
-        <v>324</v>
+        <v>305</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="s">
-        <v>325</v>
+        <v>306</v>
       </c>
       <c r="B186" s="0" t="s">
-        <v>326</v>
+        <v>307</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="B187" s="0" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="s">
-        <v>329</v>
+        <v>310</v>
       </c>
       <c r="B188" s="0" t="s">
-        <v>268</v>
+        <v>305</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="B189" s="0" t="s">
-        <v>331</v>
+        <v>312</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="B190" s="0" t="s">
-        <v>333</v>
+        <v>36</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="B191" s="0" t="s">
-        <v>335</v>
+        <v>314</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="s">
-        <v>336</v>
+        <v>315</v>
       </c>
       <c r="B192" s="0" t="s">
-        <v>117</v>
+        <v>316</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="s">
-        <v>337</v>
+        <v>317</v>
       </c>
       <c r="B193" s="0" t="s">
-        <v>338</v>
+        <v>318</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="s">
-        <v>339</v>
+        <v>319</v>
       </c>
       <c r="B194" s="0" t="s">
-        <v>340</v>
+        <v>39</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="s">
-        <v>341</v>
+        <v>320</v>
       </c>
       <c r="B195" s="0" t="s">
-        <v>342</v>
+        <v>38</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="s">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="B196" s="0" t="s">
-        <v>344</v>
+        <v>38</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="s">
-        <v>345</v>
+        <v>322</v>
       </c>
       <c r="B197" s="0" t="s">
-        <v>346</v>
+        <v>323</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="s">
-        <v>347</v>
+        <v>324</v>
       </c>
       <c r="B198" s="0" t="s">
-        <v>348</v>
+        <v>25</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="s">
-        <v>349</v>
+        <v>325</v>
       </c>
       <c r="B199" s="0" t="s">
-        <v>350</v>
+        <v>326</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
-        <v>351</v>
+        <v>327</v>
       </c>
       <c r="B200" s="0" t="s">
-        <v>352</v>
+        <v>328</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="s">
-        <v>353</v>
+        <v>329</v>
       </c>
       <c r="B201" s="0" t="s">
-        <v>354</v>
+        <v>330</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="s">
-        <v>355</v>
+        <v>331</v>
       </c>
       <c r="B202" s="0" t="s">
-        <v>356</v>
+        <v>332</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="s">
-        <v>357</v>
+        <v>333</v>
       </c>
       <c r="B203" s="0" t="s">
-        <v>358</v>
+        <v>334</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="1" t="s">
-        <v>359</v>
+        <v>335</v>
       </c>
       <c r="B204" s="0" t="s">
-        <v>53</v>
+        <v>332</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="1" t="s">
-        <v>360</v>
+        <v>336</v>
       </c>
       <c r="B205" s="0" t="s">
-        <v>361</v>
+        <v>337</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="1" t="s">
-        <v>362</v>
+        <v>338</v>
       </c>
       <c r="B206" s="0" t="s">
-        <v>208</v>
+        <v>339</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="1" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="B207" s="0" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="B208" s="0" t="s">
-        <v>366</v>
+        <v>342</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="1" t="s">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="B209" s="0" t="s">
-        <v>368</v>
+        <v>344</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="s">
-        <v>369</v>
+        <v>345</v>
       </c>
       <c r="B210" s="0" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="1" t="s">
-        <v>371</v>
+        <v>347</v>
       </c>
       <c r="B211" s="0" t="s">
-        <v>372</v>
+        <v>348</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="1" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="B212" s="0" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="1" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="B213" s="0" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="1" t="s">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="B214" s="0" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="1" t="s">
-        <v>379</v>
+        <v>355</v>
       </c>
       <c r="B215" s="0" t="s">
-        <v>380</v>
+        <v>356</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="1" t="s">
-        <v>381</v>
+        <v>357</v>
       </c>
       <c r="B216" s="0" t="s">
-        <v>382</v>
+        <v>358</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="1" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="B217" s="0" t="s">
-        <v>384</v>
+        <v>360</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="B218" s="0" t="s">
-        <v>386</v>
+        <v>6</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="1" t="s">
-        <v>387</v>
+        <v>362</v>
       </c>
       <c r="B219" s="0" t="s">
-        <v>388</v>
+        <v>363</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="1" t="s">
-        <v>389</v>
+        <v>364</v>
       </c>
       <c r="B220" s="0" t="s">
-        <v>390</v>
+        <v>10</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="1" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="B221" s="0" t="s">
-        <v>392</v>
+        <v>366</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="1" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="B222" s="0" t="s">
-        <v>261</v>
+        <v>368</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="1" t="s">
-        <v>394</v>
+        <v>369</v>
       </c>
       <c r="B223" s="0" t="s">
-        <v>395</v>
+        <v>10</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="1" t="s">
-        <v>396</v>
+        <v>370</v>
       </c>
       <c r="B224" s="0" t="s">
-        <v>397</v>
+        <v>371</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="1" t="s">
-        <v>398</v>
+        <v>372</v>
       </c>
       <c r="B225" s="0" t="s">
-        <v>399</v>
+        <v>373</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="1" t="s">
-        <v>400</v>
+        <v>374</v>
       </c>
       <c r="B226" s="0" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="1" t="s">
-        <v>402</v>
+        <v>376</v>
       </c>
       <c r="B227" s="0" t="s">
-        <v>403</v>
+        <v>9</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="1" t="s">
-        <v>404</v>
+        <v>377</v>
       </c>
       <c r="B228" s="0" t="s">
-        <v>405</v>
+        <v>8</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="1" t="s">
-        <v>406</v>
+        <v>378</v>
       </c>
       <c r="B229" s="0" t="s">
-        <v>407</v>
+        <v>379</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="1" t="s">
-        <v>408</v>
+        <v>380</v>
       </c>
       <c r="B230" s="0" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="1" t="s">
-        <v>410</v>
+        <v>382</v>
       </c>
       <c r="B231" s="0" t="s">
-        <v>411</v>
+        <v>383</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="1" t="s">
-        <v>412</v>
+        <v>384</v>
       </c>
       <c r="B232" s="0" t="s">
-        <v>413</v>
+        <v>385</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="1" t="s">
-        <v>414</v>
+        <v>386</v>
       </c>
       <c r="B233" s="0" t="s">
-        <v>415</v>
+        <v>387</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="1" t="s">
-        <v>416</v>
+        <v>388</v>
       </c>
       <c r="B234" s="0" t="s">
-        <v>417</v>
+        <v>389</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="1" t="s">
-        <v>418</v>
+        <v>390</v>
       </c>
       <c r="B235" s="0" t="s">
-        <v>0</v>
+        <v>391</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="1" t="s">
-        <v>419</v>
+        <v>392</v>
       </c>
       <c r="B236" s="0" t="s">
-        <v>420</v>
+        <v>393</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="1" t="s">
-        <v>421</v>
+        <v>394</v>
       </c>
       <c r="B237" s="0" t="s">
-        <v>422</v>
+        <v>395</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="1" t="s">
-        <v>423</v>
+        <v>396</v>
       </c>
       <c r="B238" s="0" t="s">
-        <v>424</v>
+        <v>397</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="1" t="s">
-        <v>425</v>
+        <v>398</v>
       </c>
       <c r="B239" s="0" t="s">
-        <v>426</v>
+        <v>287</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="1" t="s">
-        <v>427</v>
+        <v>399</v>
       </c>
       <c r="B240" s="0" t="s">
-        <v>428</v>
+        <v>400</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="1" t="s">
-        <v>429</v>
+        <v>401</v>
       </c>
       <c r="B241" s="0" t="s">
-        <v>430</v>
+        <v>402</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="1" t="s">
-        <v>431</v>
+        <v>403</v>
       </c>
       <c r="B242" s="0" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="243" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="1" t="s">
-        <v>433</v>
+        <v>405</v>
       </c>
       <c r="B243" s="0" t="s">
-        <v>434</v>
+        <v>406</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="1" t="s">
-        <v>435</v>
+        <v>407</v>
       </c>
       <c r="B244" s="0" t="s">
-        <v>306</v>
+        <v>408</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="1" t="s">
-        <v>436</v>
+        <v>409</v>
       </c>
       <c r="B245" s="0" t="s">
-        <v>437</v>
+        <v>410</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="1" t="s">
-        <v>438</v>
+        <v>411</v>
       </c>
       <c r="B246" s="0" t="s">
-        <v>439</v>
+        <v>412</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="1" t="s">
-        <v>440</v>
+        <v>413</v>
       </c>
       <c r="B247" s="0" t="s">
-        <v>441</v>
+        <v>414</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="1" t="s">
-        <v>442</v>
+        <v>415</v>
       </c>
       <c r="B248" s="0" t="s">
-        <v>443</v>
+        <v>416</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="1" t="s">
-        <v>444</v>
+        <v>417</v>
       </c>
       <c r="B249" s="0" t="s">
-        <v>445</v>
+        <v>418</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="1" t="s">
-        <v>446</v>
+        <v>419</v>
       </c>
       <c r="B250" s="0" t="s">
-        <v>447</v>
+        <v>420</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="1" t="s">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="B251" s="0" t="s">
-        <v>449</v>
+        <v>422</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="1" t="s">
-        <v>450</v>
+        <v>423</v>
       </c>
       <c r="B252" s="0" t="s">
-        <v>451</v>
+        <v>424</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="1" t="s">
-        <v>452</v>
+        <v>425</v>
       </c>
       <c r="B253" s="0" t="s">
-        <v>453</v>
+        <v>426</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="1" t="s">
-        <v>454</v>
+        <v>427</v>
       </c>
       <c r="B254" s="0" t="s">
-        <v>455</v>
+        <v>428</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="1" t="s">
-        <v>456</v>
+        <v>429</v>
       </c>
       <c r="B255" s="0" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="1" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="B256" s="0" t="s">
-        <v>458</v>
+        <v>432</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="1" t="s">
-        <v>459</v>
+        <v>433</v>
       </c>
       <c r="B257" s="0" t="s">
-        <v>460</v>
+        <v>434</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="1" t="s">
-        <v>461</v>
+        <v>435</v>
       </c>
       <c r="B258" s="0" t="s">
-        <v>462</v>
+        <v>436</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="1" t="s">
-        <v>463</v>
+        <v>437</v>
       </c>
       <c r="B259" s="0" t="s">
-        <v>462</v>
+        <v>438</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="1" t="s">
-        <v>464</v>
+        <v>439</v>
       </c>
       <c r="B260" s="0" t="s">
-        <v>465</v>
+        <v>440</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="1" t="s">
-        <v>466</v>
+        <v>441</v>
       </c>
       <c r="B261" s="0" t="s">
-        <v>467</v>
+        <v>442</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="1" t="s">
-        <v>468</v>
+        <v>443</v>
       </c>
       <c r="B262" s="0" t="s">
-        <v>467</v>
+        <v>444</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="1" t="s">
-        <v>469</v>
+        <v>445</v>
       </c>
       <c r="B263" s="0" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="264" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="1" t="s">
-        <v>471</v>
+        <v>447</v>
       </c>
       <c r="B264" s="0" t="s">
-        <v>236</v>
+        <v>448</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="1" t="s">
-        <v>472</v>
+        <v>449</v>
       </c>
       <c r="B265" s="0" t="s">
-        <v>473</v>
+        <v>450</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="1" t="s">
-        <v>474</v>
+        <v>451</v>
       </c>
       <c r="B266" s="0" t="s">
-        <v>475</v>
+        <v>452</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="1" t="s">
-        <v>476</v>
+        <v>453</v>
       </c>
       <c r="B267" s="0" t="s">
-        <v>477</v>
+        <v>454</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="1" t="s">
-        <v>478</v>
+        <v>455</v>
       </c>
       <c r="B268" s="0" t="s">
-        <v>479</v>
+        <v>456</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="1" t="s">
-        <v>480</v>
+        <v>457</v>
       </c>
       <c r="B269" s="0" t="s">
-        <v>481</v>
+        <v>458</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="1" t="s">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="B270" s="0" t="s">
-        <v>8</v>
+        <v>460</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="1" t="s">
-        <v>483</v>
+        <v>461</v>
       </c>
       <c r="B271" s="0" t="s">
-        <v>484</v>
+        <v>462</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="1" t="s">
-        <v>485</v>
+        <v>463</v>
       </c>
       <c r="B272" s="0" t="s">
-        <v>486</v>
+        <v>464</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="1" t="s">
-        <v>487</v>
+        <v>465</v>
       </c>
       <c r="B273" s="0" t="s">
-        <v>486</v>
+        <v>466</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="1" t="s">
-        <v>488</v>
+        <v>467</v>
       </c>
       <c r="B274" s="0" t="s">
-        <v>489</v>
+        <v>468</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="1" t="s">
-        <v>490</v>
+        <v>469</v>
       </c>
       <c r="B275" s="0" t="s">
-        <v>491</v>
+        <v>470</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="1" t="s">
-        <v>492</v>
+        <v>471</v>
       </c>
       <c r="B276" s="0" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="277" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="1" t="s">
-        <v>494</v>
+        <v>473</v>
       </c>
       <c r="B277" s="0" t="s">
-        <v>495</v>
+        <v>448</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="1" t="s">
-        <v>496</v>
+        <v>474</v>
       </c>
       <c r="B278" s="0" t="s">
-        <v>83</v>
+        <v>475</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="1" t="s">
-        <v>497</v>
+        <v>476</v>
       </c>
       <c r="B279" s="0" t="s">
-        <v>498</v>
+        <v>477</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="1" t="s">
-        <v>499</v>
+        <v>478</v>
       </c>
       <c r="B280" s="0" t="s">
-        <v>500</v>
+        <v>479</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="1" t="s">
-        <v>501</v>
+        <v>480</v>
       </c>
       <c r="B281" s="0" t="s">
-        <v>502</v>
+        <v>479</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="1" t="s">
-        <v>503</v>
+        <v>481</v>
       </c>
       <c r="B282" s="0" t="s">
-        <v>504</v>
+        <v>482</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A283" s="0" t="s">
-        <v>505</v>
+      <c r="A283" s="1" t="s">
+        <v>483</v>
       </c>
       <c r="B283" s="0" t="s">
-        <v>506</v>
+        <v>201</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="1" t="s">
-        <v>507</v>
+        <v>484</v>
       </c>
       <c r="B284" s="0" t="s">
-        <v>508</v>
+        <v>485</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="1" t="s">
-        <v>509</v>
+        <v>486</v>
       </c>
       <c r="B285" s="0" t="s">
-        <v>411</v>
+        <v>487</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="1" t="s">
-        <v>510</v>
+        <v>488</v>
       </c>
       <c r="B286" s="0" t="s">
-        <v>511</v>
+        <v>487</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="1" t="s">
-        <v>512</v>
+        <v>489</v>
       </c>
       <c r="B287" s="0" t="s">
-        <v>282</v>
+        <v>490</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="1" t="s">
-        <v>513</v>
+        <v>491</v>
       </c>
       <c r="B288" s="0" t="s">
-        <v>514</v>
+        <v>492</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="1" t="s">
-        <v>515</v>
+        <v>493</v>
       </c>
       <c r="B289" s="0" t="s">
-        <v>516</v>
+        <v>494</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="1" t="s">
-        <v>517</v>
+        <v>495</v>
       </c>
       <c r="B290" s="0" t="s">
-        <v>518</v>
+        <v>496</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="1" t="s">
-        <v>519</v>
+        <v>497</v>
       </c>
       <c r="B291" s="0" t="s">
-        <v>208</v>
+        <v>498</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="1" t="s">
-        <v>520</v>
+        <v>499</v>
       </c>
       <c r="B292" s="0" t="s">
-        <v>125</v>
+        <v>498</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="1" t="s">
-        <v>521</v>
+        <v>500</v>
       </c>
       <c r="B293" s="0" t="s">
-        <v>460</v>
+        <v>498</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="1" t="s">
-        <v>522</v>
+        <v>501</v>
       </c>
       <c r="B294" s="0" t="s">
-        <v>523</v>
+        <v>502</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="1" t="s">
-        <v>524</v>
+        <v>503</v>
       </c>
       <c r="B295" s="0" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="1" t="s">
-        <v>525</v>
+        <v>504</v>
       </c>
       <c r="B296" s="0" t="s">
-        <v>111</v>
+        <v>505</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="1" t="s">
-        <v>526</v>
+        <v>506</v>
       </c>
       <c r="B297" s="0" t="s">
-        <v>527</v>
+        <v>507</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="B298" s="0" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A299" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B299" s="0" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A300" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B300" s="0" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A301" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B301" s="0" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="302" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A302" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="B302" s="0" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A303" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B303" s="0" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A304" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B304" s="0" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A305" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="B305" s="0" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A306" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="B306" s="0" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A307" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="B307" s="0" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A308" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="B308" s="0" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A309" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="B309" s="0" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A310" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="B310" s="0" t="s">
         <v>528</v>
       </c>
-      <c r="B298" s="0" t="s">
-        <v>38</v>
+    </row>
+    <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A311" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="B311" s="0" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A312" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="B312" s="0" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A313" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B313" s="0" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A314" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="B314" s="0" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A315" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B315" s="0" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A316" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B316" s="0" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A317" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="B317" s="0" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A318" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B318" s="0" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A319" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B319" s="0" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A320" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B320" s="0" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A321" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B321" s="0" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A322" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B322" s="0" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A323" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B323" s="0" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A324" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="B324" s="0" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A325" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B325" s="0" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A326" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="B326" s="0" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A327" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="B327" s="0" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A328" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B328" s="0" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A329" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B329" s="0" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A330" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="B330" s="0" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A331" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="B331" s="0" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A332" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B332" s="0" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A333" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B333" s="0" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A334" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="B334" s="0" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A335" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="B335" s="0" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A336" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B336" s="0" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A337" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="B337" s="0" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A338" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="B338" s="0" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A339" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="B339" s="0" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A340" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B340" s="0" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A341" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="B341" s="0" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A342" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B342" s="0" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A343" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="B343" s="0" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A344" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="B344" s="0" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A345" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="B345" s="0" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A346" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="B346" s="0" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A347" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="B347" s="0" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A348" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="B348" s="0" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A349" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="B349" s="0" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A350" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B350" s="0" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A351" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="B351" s="0" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A352" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B352" s="0" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A353" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="B353" s="0" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A354" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="B354" s="0" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A355" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B355" s="0" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A356" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="B356" s="0" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A357" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="B357" s="0" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A358" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="B358" s="0" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A359" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B359" s="0" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A360" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="B360" s="0" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A361" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="B361" s="0" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A362" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="B362" s="0" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A363" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="B363" s="0" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A364" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="B364" s="0" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A365" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="B365" s="0" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A366" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B366" s="0" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A367" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B367" s="0" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A368" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B368" s="0" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A369" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="B369" s="0" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A370" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="B370" s="0" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A371" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="B371" s="0" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A372" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="B372" s="0" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A373" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="B373" s="0" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A374" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="B374" s="0" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A375" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="B375" s="0" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A376" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="B376" s="0" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A377" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B377" s="0" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A378" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="B378" s="0" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A379" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B379" s="0" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A380" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="B380" s="0" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A381" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="B381" s="0" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A382" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B382" s="0" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A383" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="B383" s="0" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A384" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B384" s="0" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A385" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="B385" s="0" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A386" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="B386" s="0" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A387" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B387" s="0" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="388" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A388" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="B388" s="0" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A389" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B389" s="0" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A390" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="B390" s="0" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="391" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A391" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="B391" s="0" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="392" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A392" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="B392" s="0" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="393" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A393" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="B393" s="0" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="394" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A394" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="B394" s="0" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A395" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="B395" s="0" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="396" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A396" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="B396" s="0" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A397" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="B397" s="0" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A398" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="B398" s="0" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A399" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="B399" s="0" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A400" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="B400" s="0" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A401" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="B401" s="0" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A402" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="B402" s="0" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A403" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="B403" s="0" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A404" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B404" s="0" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="405" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A405" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="B405" s="0" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="406" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A406" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="B406" s="0" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="407" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A407" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="B407" s="0" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="408" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A408" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="B408" s="0" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A409" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B409" s="0" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="410" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A410" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="B410" s="0" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A411" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="B411" s="0" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A412" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B412" s="0" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="413" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A413" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="B413" s="0" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="414" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A414" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="B414" s="0" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A415" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="B415" s="0" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="416" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A416" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="B416" s="0" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A417" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="B417" s="0" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A418" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="B418" s="0" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A419" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="B419" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A420" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="B420" s="0" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A421" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="B421" s="0" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A422" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="B422" s="0" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A423" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="B423" s="0" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A424" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="B424" s="0" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A425" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="B425" s="0" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A426" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="B426" s="0" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A427" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B427" s="0" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A428" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="B428" s="0" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A429" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="B429" s="0" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A430" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="B430" s="0" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="431" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A431" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="B431" s="0" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="432" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A432" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="B432" s="0" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="433" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A433" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="B433" s="0" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A434" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="B434" s="0" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="435" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A435" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="B435" s="0" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="436" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A436" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="B436" s="0" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="437" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A437" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="B437" s="0" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A438" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="B438" s="0" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="439" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A439" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="B439" s="0" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="440" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A440" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="B440" s="0" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A441" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="B441" s="0" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A442" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="B442" s="0" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A443" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="B443" s="0" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A444" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="B444" s="0" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A445" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="B445" s="0" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A446" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="B446" s="0" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="447" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A447" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="B447" s="0" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A448" s="0" t="s">
+        <v>775</v>
+      </c>
+      <c r="B448" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="449" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A449" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="B449" s="0" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A450" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="B450" s="0" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A451" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="B451" s="0" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A452" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="B452" s="0" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A453" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="B453" s="0" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A454" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="B454" s="0" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A455" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="B455" s="0" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A456" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="B456" s="0" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A457" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="B457" s="0" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A458" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="B458" s="0" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A459" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="B459" s="0" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A460" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B460" s="0" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="461" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A461" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="B461" s="0" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="462" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A462" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="B462" s="0" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A463" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="B463" s="0" t="s">
+        <v>412</v>
       </c>
     </row>
   </sheetData>
